--- a/output/pdf_financials_xlsx/OSM.xlsx
+++ b/output/pdf_financials_xlsx/OSM.xlsx
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.074422</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.210281</v>
@@ -712,13 +712,13 @@
         <v>0.847233</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.887159</v>
+        <v>2.289629</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.397568</v>
+        <v>0.752887</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.331932</v>
+        <v>0.41514</v>
       </c>
     </row>
     <row r="11">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-0.074422</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-0.210281</v>
@@ -762,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.008433</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -771,10 +771,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.025436</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.00208</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1295,7 +1295,7 @@
         <v>-0.074422</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.206857</v>
+        <v>-0.21529</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.206857</v>
@@ -1304,10 +1304,10 @@
         <v>-2.222838</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.530761</v>
+        <v>-2.505325</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.394461</v>
+        <v>-2.396541</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-2.199848</v>
@@ -1357,7 +1357,7 @@
         <v>-0.074422</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.206717</v>
+        <v>-0.21515</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.206857</v>
@@ -1366,10 +1366,10 @@
         <v>-2.222838</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.529916</v>
+        <v>-2.50448</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.393757</v>
+        <v>-2.395837</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-2.199848</v>
@@ -1535,10 +1535,10 @@
         <v>0.063026</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.004463</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.00141</v>
       </c>
     </row>
     <row r="35">
@@ -1597,10 +1597,10 @@
         <v>0.063026</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.004463</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.00141</v>
       </c>
     </row>
     <row r="37">
@@ -1969,10 +1969,10 @@
         <v>0.07793799999999999</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.008383</v>
+        <v>0.00392</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.00533</v>
+        <v>0.00392</v>
       </c>
     </row>
     <row r="49">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14068,7 +14068,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E212" s="5" t="n">

--- a/output/pdf_financials_xlsx/OSM.xlsx
+++ b/output/pdf_financials_xlsx/OSM.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>0.009809</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0</v>
@@ -4650,10 +4650,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
@@ -4763,10 +4761,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.415617</v>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
@@ -4881,7 +4877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L230"/>
+  <dimension ref="A1:L241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10766,7 +10762,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -11624,7 +11624,11 @@
           <t>Residual value of warrants issued in unit private placement</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -12687,28 +12691,26 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Net loss $</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>-0.074422</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12725,44 +12727,50 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I140" s="5" t="n">
-        <v>0.155365</v>
-      </c>
-      <c r="J140" s="5" t="n">
-        <v>0.116427</v>
-      </c>
-      <c r="K140" s="5" t="n">
-        <v>0.07999100000000001</v>
-      </c>
-      <c r="L140" s="5" t="n">
-        <v>0.070391</v>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Consulting 8</t>
+          <t>Accrued liabilities</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="n">
+        <v>0.064</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12784,37 +12792,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J141" s="5" t="n">
-        <v>0.785313</v>
-      </c>
-      <c r="K141" s="5" t="n">
-        <v>0.369582</v>
-      </c>
-      <c r="L141" s="5" t="n">
-        <v>0.297101</v>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Share-based compensation 7</t>
+          <t>Issuance of common shares, net of fees</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E142" s="5" t="n">
+        <v>0.431039</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12836,11 +12848,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J142" s="5" t="n">
-        <v>0.247485</v>
-      </c>
-      <c r="K142" s="5" t="n">
-        <v>0.050117</v>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -12851,22 +12867,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Filing fees</t>
+          <t>Cash beginning of year</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -12889,40 +12905,50 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I143" s="5" t="n">
-        <v>0.096099</v>
-      </c>
-      <c r="J143" s="5" t="n">
-        <v>0.101846</v>
-      </c>
-      <c r="K143" s="5" t="n">
-        <v>0.027986</v>
-      </c>
-      <c r="L143" s="5" t="n">
-        <v>0.034831</v>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Travel and entertainment</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash end of year $</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="n">
+        <v>0.415617</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12939,14 +12965,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I144" s="5" t="n">
-        <v>0.204403</v>
-      </c>
-      <c r="J144" s="5" t="n">
-        <v>0.115281</v>
-      </c>
-      <c r="K144" s="5" t="n">
-        <v>0.01423</v>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -12967,12 +12999,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Marketing expenses</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>MarketingExpense</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -12996,18 +13028,16 @@
         </is>
       </c>
       <c r="I145" s="5" t="n">
-        <v>1.039869</v>
+        <v>0.155365</v>
       </c>
       <c r="J145" s="5" t="n">
-        <v>0.780006</v>
+        <v>0.116427</v>
       </c>
       <c r="K145" s="5" t="n">
-        <v>0.082839</v>
-      </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.07999100000000001</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>0.070391</v>
       </c>
     </row>
     <row r="146">
@@ -13023,10 +13053,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>General and office</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
+          <t>Consulting 8</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -13047,17 +13081,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I146" s="5" t="n">
-        <v>0.242855</v>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J146" s="5" t="n">
-        <v>0.10354</v>
+        <v>0.785313</v>
       </c>
       <c r="K146" s="5" t="n">
-        <v>0.109251</v>
+        <v>0.369582</v>
       </c>
       <c r="L146" s="5" t="n">
-        <v>0.022833</v>
+        <v>0.297101</v>
       </c>
     </row>
     <row r="147">
@@ -13073,14 +13109,10 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>ForeignExchangeTradingGains</t>
-        </is>
-      </c>
+          <t>Share-based compensation 7</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -13107,13 +13139,15 @@
         </is>
       </c>
       <c r="J147" s="5" t="n">
-        <v>0.039027</v>
+        <v>0.247485</v>
       </c>
       <c r="K147" s="5" t="n">
-        <v>0.018891</v>
-      </c>
-      <c r="L147" s="5" t="n">
-        <v>-0.010016</v>
+        <v>0.050117</v>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="148">
@@ -13129,12 +13163,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Total expenses</t>
+          <t>Filing fees</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13157,21 +13191,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I148" s="5" t="n">
+        <v>0.096099</v>
+      </c>
+      <c r="J148" s="5" t="n">
+        <v>0.101846</v>
       </c>
       <c r="K148" s="5" t="n">
-        <v>0.752887</v>
+        <v>0.027986</v>
       </c>
       <c r="L148" s="5" t="n">
-        <v>0.41514</v>
+        <v>0.034831</v>
       </c>
     </row>
     <row r="149">
@@ -13187,14 +13217,10 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Net loss before other items</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Travel and entertainment</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -13215,19 +13241,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I149" s="5" t="n">
+        <v>0.204403</v>
       </c>
       <c r="J149" s="5" t="n">
-        <v>-2.289629</v>
+        <v>0.115281</v>
       </c>
       <c r="K149" s="5" t="n">
-        <v>-0.752887</v>
-      </c>
-      <c r="L149" s="5" t="n">
-        <v>-0.41514</v>
+        <v>0.01423</v>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="150">
@@ -13243,10 +13269,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Recovery of input tax credits</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
+          <t>Marketing expenses</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>MarketingExpense</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -13267,18 +13297,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I150" s="5" t="n">
+        <v>1.039869</v>
+      </c>
+      <c r="J150" s="5" t="n">
+        <v>0.780006</v>
       </c>
       <c r="K150" s="5" t="n">
-        <v>0.005638</v>
+        <v>0.082839</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -13299,14 +13325,10 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Other income</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>General and office</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -13327,21 +13349,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I151" s="5" t="n">
+        <v>0.242855</v>
       </c>
       <c r="J151" s="5" t="n">
-        <v>0.003981</v>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.10354</v>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>0.109251</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>0.04617</v>
+        <v>0.022833</v>
       </c>
     </row>
     <row r="152">
@@ -13357,10 +13375,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Finance charges 5</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>Foreign exchange</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -13386,16 +13408,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J152" s="5" t="n">
+        <v>0.039027</v>
       </c>
       <c r="K152" s="5" t="n">
-        <v>-0.002902</v>
+        <v>0.018891</v>
       </c>
       <c r="L152" s="5" t="n">
-        <v>-0.00856</v>
+        <v>-0.010016</v>
       </c>
     </row>
     <row r="153">
@@ -13411,10 +13431,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Recovery of license purchase payable 4</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -13446,12 +13470,10 @@
         </is>
       </c>
       <c r="K153" s="5" t="n">
-        <v>0.28778</v>
-      </c>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.752887</v>
+      </c>
+      <c r="L153" s="5" t="n">
+        <v>0.41514</v>
       </c>
     </row>
     <row r="154">
@@ -13467,10 +13489,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Impairment of other receivable 8</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr"/>
+          <t>Net loss before other items</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -13496,18 +13522,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J154" s="5" t="n">
+        <v>-2.289629</v>
       </c>
       <c r="K154" s="5" t="n">
-        <v>-0.03836</v>
-      </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.752887</v>
+      </c>
+      <c r="L154" s="5" t="n">
+        <v>-0.41514</v>
       </c>
     </row>
     <row r="155">
@@ -13523,7 +13545,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets 4</t>
+          <t>Recovery of input tax credits</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -13558,7 +13580,7 @@
         </is>
       </c>
       <c r="K155" s="5" t="n">
-        <v>-1.775884</v>
+        <v>0.005638</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -13579,10 +13601,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Gain on debt settlement 7</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -13608,16 +13634,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K156" s="5" t="n">
-        <v>0.076767</v>
+      <c r="J156" s="5" t="n">
+        <v>0.003981</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L156" s="5" t="n">
-        <v>0.03</v>
+        <v>0.04617</v>
       </c>
     </row>
     <row r="157">
@@ -13633,14 +13659,10 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Net Loss</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Finance charges 5</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -13666,14 +13688,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J157" s="5" t="n">
-        <v>-2.394461</v>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K157" s="5" t="n">
-        <v>-2.199848</v>
+        <v>-0.002902</v>
       </c>
       <c r="L157" s="5" t="n">
-        <v>-0.34753</v>
+        <v>-0.00856</v>
       </c>
     </row>
     <row r="158">
@@ -13689,7 +13713,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Foreign currency translation adjustment</t>
+          <t>Recovery of license purchase payable 4</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -13713,17 +13737,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I158" s="5" t="n">
-        <v>-0.165168</v>
-      </c>
-      <c r="J158" s="5" t="n">
-        <v>-0.032856</v>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K158" s="5" t="n">
-        <v>0.101432</v>
-      </c>
-      <c r="L158" s="5" t="n">
-        <v>0.015254</v>
+        <v>0.28778</v>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="159">
@@ -13739,7 +13769,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Comprehensive loss</t>
+          <t>Impairment of other receivable 8</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -13763,17 +13793,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I159" s="5" t="n">
-        <v>-2.695929</v>
-      </c>
-      <c r="J159" s="5" t="n">
-        <v>-2.427317</v>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K159" s="5" t="n">
-        <v>-2.098416</v>
-      </c>
-      <c r="L159" s="5" t="n">
-        <v>-0.332276</v>
+        <v>-0.03836</v>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="160">
@@ -13789,7 +13825,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Basic and diluted net loss per share</t>
+          <t>Impairment of exploration and evaluation assets 4</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -13813,17 +13849,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I160" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="J160" s="5" t="n">
-        <v>-4e-08</v>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K160" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="L160" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-1.775884</v>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="161">
@@ -13839,14 +13881,10 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Gain on debt settlement 7</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -13867,17 +13905,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I161" s="5" t="n">
-        <v>60.364716</v>
-      </c>
-      <c r="J161" s="5" t="n">
-        <v>62.516414</v>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K161" s="5" t="n">
-        <v>65.58807400000001</v>
+        <v>0.076767</v>
       </c>
       <c r="L161" s="5" t="n">
-        <v>67.26880800000001</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="162">
@@ -13893,12 +13935,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Depreciation 3</t>
+          <t>Net Loss</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -13921,21 +13963,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I162" s="5" t="n">
-        <v>0.000845</v>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J162" s="5" t="n">
-        <v>0.000704</v>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.394461</v>
+      </c>
+      <c r="K162" s="5" t="n">
+        <v>-2.199848</v>
+      </c>
+      <c r="L162" s="5" t="n">
+        <v>-0.34753</v>
       </c>
     </row>
     <row r="163">
@@ -13951,14 +13991,10 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Total Expenses</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Foreign currency translation adjustment</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -13979,21 +14015,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I163" s="5" t="n">
+        <v>-0.165168</v>
       </c>
       <c r="J163" s="5" t="n">
-        <v>2.289629</v>
+        <v>-0.032856</v>
       </c>
       <c r="K163" s="5" t="n">
-        <v>0.752887</v>
-      </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.101432</v>
+      </c>
+      <c r="L163" s="5" t="n">
+        <v>0.015254</v>
       </c>
     </row>
     <row r="164">
@@ -14009,7 +14041,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Write down of input tax credits</t>
+          <t>Comprehensive loss</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -14033,21 +14065,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I164" s="5" t="n">
+        <v>-2.695929</v>
       </c>
       <c r="J164" s="5" t="n">
-        <v>-0.110893</v>
+        <v>-2.427317</v>
       </c>
       <c r="K164" s="5" t="n">
-        <v>0.005638</v>
-      </c>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.098416</v>
+      </c>
+      <c r="L164" s="5" t="n">
+        <v>-0.332276</v>
       </c>
     </row>
     <row r="165">
@@ -14063,14 +14091,10 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Basic and diluted net loss per share</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -14092,20 +14116,16 @@
         </is>
       </c>
       <c r="I165" s="5" t="n">
-        <v>-0.025436</v>
+        <v>-4e-08</v>
       </c>
       <c r="J165" s="5" t="n">
-        <v>0.00208</v>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4e-08</v>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="L165" s="5" t="n">
+        <v>-1e-08</v>
       </c>
     </row>
     <row r="166">
@@ -14121,10 +14141,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Impairment of other receivable</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -14145,21 +14169,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I166" s="5" t="n">
+        <v>60.364716</v>
       </c>
       <c r="J166" s="5" t="n">
-        <v>-0.03836</v>
+        <v>62.516414</v>
       </c>
       <c r="K166" s="5" t="n">
-        <v>8e-06</v>
-      </c>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>65.58807400000001</v>
+      </c>
+      <c r="L166" s="5" t="n">
+        <v>67.26880800000001</v>
       </c>
     </row>
     <row r="167">
@@ -14175,12 +14195,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Consulting 7</t>
+          <t>Depreciation 3</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -14204,10 +14224,10 @@
         </is>
       </c>
       <c r="I167" s="5" t="n">
-        <v>0.751134</v>
+        <v>0.000845</v>
       </c>
       <c r="J167" s="5" t="n">
-        <v>0.785313</v>
+        <v>0.000704</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
@@ -14233,10 +14253,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Stock based compensation 6</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr"/>
+          <t>Total Expenses</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -14257,16 +14281,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I168" s="5" t="n">
-        <v>0.065078</v>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J168" s="5" t="n">
-        <v>0.247485</v>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.289629</v>
+      </c>
+      <c r="K168" s="5" t="n">
+        <v>0.752887</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
@@ -14287,7 +14311,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Uncollectible input tax credits</t>
+          <t>Write down of input tax credits</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -14317,12 +14341,10 @@
         </is>
       </c>
       <c r="J169" s="5" t="n">
-        <v>0.110893</v>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.110893</v>
+      </c>
+      <c r="K169" s="5" t="n">
+        <v>0.005638</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -14343,12 +14365,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Foreign exchange (gain) or loss</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -14372,10 +14394,10 @@
         </is>
       </c>
       <c r="I170" s="5" t="n">
-        <v>0.000549</v>
+        <v>-0.025436</v>
       </c>
       <c r="J170" s="5" t="n">
-        <v>0.039027</v>
+        <v>0.00208</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -14401,14 +14423,10 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Impairment of other receivable</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -14429,16 +14447,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I171" s="5" t="n">
-        <v>-2.530761</v>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J171" s="5" t="n">
-        <v>-2.394461</v>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.03836</v>
+      </c>
+      <c r="K171" s="5" t="n">
+        <v>8e-06</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -14454,17 +14472,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Consulting 7</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -14482,16 +14500,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H172" s="5" t="n">
-        <v>0.916483</v>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I172" s="5" t="n">
-        <v>0.9064990000000001</v>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.751134</v>
+      </c>
+      <c r="J172" s="5" t="n">
+        <v>0.785313</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -14512,12 +14530,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Stock based compensation</t>
+          <t>Stock based compensation 6</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -14536,16 +14554,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H173" s="5" t="n">
-        <v>0.268261</v>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I173" s="5" t="n">
         <v>0.065078</v>
       </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J173" s="5" t="n">
+        <v>0.247485</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -14566,19 +14584,15 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Filing fees</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Uncollectible input tax credits</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -14594,16 +14608,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H174" s="5" t="n">
-        <v>0.103794</v>
-      </c>
-      <c r="I174" s="5" t="n">
-        <v>0.096099</v>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J174" s="5" t="n">
+        <v>0.110893</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -14624,15 +14640,19 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Travel and accommodation</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>Foreign exchange (gain) or loss</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -14654,12 +14674,10 @@
         </is>
       </c>
       <c r="I175" s="5" t="n">
-        <v>0.204403</v>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000549</v>
+      </c>
+      <c r="J175" s="5" t="n">
+        <v>0.039027</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
@@ -14680,17 +14698,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>General and administrative expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Marketing expenses</t>
+          <t>Net loss</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>MarketingExpense</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -14708,16 +14726,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H176" s="5" t="n">
-        <v>0.728247</v>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I176" s="5" t="n">
-        <v>1.039869</v>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.530761</v>
+      </c>
+      <c r="J176" s="5" t="n">
+        <v>-2.394461</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
@@ -14743,10 +14761,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>General and office</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -14763,10 +14785,10 @@
         </is>
       </c>
       <c r="H177" s="5" t="n">
-        <v>0.203583</v>
+        <v>0.916483</v>
       </c>
       <c r="I177" s="5" t="n">
-        <v>0.2437</v>
+        <v>0.9064990000000001</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
@@ -14797,7 +14819,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Gain on accounts payable write off</t>
+          <t>Stock based compensation</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -14817,12 +14839,10 @@
         </is>
       </c>
       <c r="H178" s="5" t="n">
-        <v>-0.017375</v>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.268261</v>
+      </c>
+      <c r="I178" s="5" t="n">
+        <v>0.065078</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -14853,14 +14873,16 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Interest (income) expense</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Filing fees</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="n">
+        <v>0.009809</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14872,13 +14894,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H179" s="5" t="n">
+        <v>0.103794</v>
       </c>
       <c r="I179" s="5" t="n">
-        <v>-0.025436</v>
+        <v>0.096099</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -14909,14 +14929,10 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Foreign exchange (gain) or loss</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Travel and accommodation</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -14932,11 +14948,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H180" s="5" t="n">
-        <v>0.019845</v>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I180" s="5" t="n">
-        <v>0.000549</v>
+        <v>0.204403</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
@@ -14967,12 +14985,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Net loss for the period</t>
+          <t>Marketing expenses</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>MarketingExpense</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -14991,10 +15009,10 @@
         </is>
       </c>
       <c r="H181" s="5" t="n">
-        <v>-2.222838</v>
+        <v>0.728247</v>
       </c>
       <c r="I181" s="5" t="n">
-        <v>-2.530761</v>
+        <v>1.039869</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
@@ -15025,7 +15043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Cumulative translation adjustment</t>
+          <t>General and office</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -15045,10 +15063,10 @@
         </is>
       </c>
       <c r="H182" s="5" t="n">
-        <v>0.006721</v>
+        <v>0.203583</v>
       </c>
       <c r="I182" s="5" t="n">
-        <v>-0.165168</v>
+        <v>0.2437</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
@@ -15079,14 +15097,10 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the period</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Gain on accounts payable write off</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -15103,10 +15117,12 @@
         </is>
       </c>
       <c r="H183" s="5" t="n">
-        <v>-2.216117</v>
-      </c>
-      <c r="I183" s="5" t="n">
-        <v>-2.695929</v>
+        <v>-0.017375</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
@@ -15137,7 +15153,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Basic and diluted net loss per share 7</t>
+          <t>Interest (income) expense</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -15156,11 +15172,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H184" s="5" t="n">
-        <v>-4e-08</v>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I184" s="5" t="n">
-        <v>-4e-08</v>
+        <v>-0.025436</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
@@ -15186,17 +15204,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares total</t>
+          <t>Foreign exchange (gain) or loss</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -15215,10 +15233,10 @@
         </is>
       </c>
       <c r="H185" s="5" t="n">
-        <v>56.979068</v>
+        <v>0.019845</v>
       </c>
       <c r="I185" s="5" t="n">
-        <v>60.364716</v>
+        <v>0.000549</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
@@ -15244,15 +15262,19 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Due Diligence cost</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Due Diligence cost total</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
+          <t>Net loss for the period</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -15263,18 +15285,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G186" s="5" t="n">
-        <v>0.045265</v>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H186" s="5" t="n">
+        <v>-2.222838</v>
+      </c>
+      <c r="I186" s="5" t="n">
+        <v>-2.530761</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -15300,12 +15320,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Professional fees total</t>
+          <t>Cumulative translation adjustment</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -15314,21 +15334,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F187" s="5" t="n">
-        <v>0.014793</v>
-      </c>
-      <c r="G187" s="5" t="n">
-        <v>0.08550199999999999</v>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H187" s="5" t="n">
+        <v>0.006721</v>
+      </c>
+      <c r="I187" s="5" t="n">
+        <v>-0.165168</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
@@ -15354,35 +15374,39 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Filing fees</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Filing fees total</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr"/>
+          <t>Comprehensive loss for the period</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F188" s="5" t="n">
-        <v>0.016595</v>
-      </c>
-      <c r="G188" s="5" t="n">
-        <v>0.033907</v>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H188" s="5" t="n">
+        <v>-2.216117</v>
+      </c>
+      <c r="I188" s="5" t="n">
+        <v>-2.695929</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -15408,12 +15432,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Stock based compensation</t>
+          <t>General and administrative expenses</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Stock based compensation total</t>
+          <t>Basic and diluted net loss per share 7</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -15422,23 +15446,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F189" s="5" t="n">
-        <v>0.142649</v>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H189" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="I189" s="5" t="n">
+        <v>-4e-08</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
@@ -15464,35 +15486,39 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Office and administration</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Office and administration total</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr"/>
+          <t>Weighted average number of common shares total</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F190" s="5" t="n">
-        <v>0.036244</v>
-      </c>
-      <c r="G190" s="5" t="n">
-        <v>0.040492</v>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H190" s="5" t="n">
+        <v>56.979068</v>
+      </c>
+      <c r="I190" s="5" t="n">
+        <v>60.364716</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
@@ -15518,29 +15544,27 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Total expenses</t>
+          <t>Due Diligence cost</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Total expenses total</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Due Diligence cost total</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F191" s="5" t="n">
-        <v>0.210281</v>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G191" s="5" t="n">
-        <v>0.224056</v>
+        <v>0.045265</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -15576,29 +15600,25 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Interest income total</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>InterestIncome</t>
-        </is>
-      </c>
+          <t>Professional fees total</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F192" s="5" t="n">
-        <v>0.008433</v>
+        <v>0.014793</v>
       </c>
       <c r="G192" s="5" t="n">
-        <v>0.017199</v>
+        <v>0.08550199999999999</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -15634,29 +15654,25 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Filing fees</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Filing fees total</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F193" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.016595</v>
       </c>
       <c r="G193" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.033907</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -15692,12 +15708,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Stock based compensation</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted</t>
+          <t>Stock based compensation total</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -15707,10 +15723,12 @@
         </is>
       </c>
       <c r="F194" s="5" t="n">
-        <v>8.598901</v>
-      </c>
-      <c r="G194" s="5" t="n">
-        <v>10</v>
+        <v>0.142649</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -15746,12 +15764,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Office and administration</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Balance as at December 31, 19,030,780 1,265,595 195,556</t>
+          <t>Office and administration total</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -15761,10 +15779,10 @@
         </is>
       </c>
       <c r="F195" s="5" t="n">
-        <v>1.184881</v>
+        <v>0.036244</v>
       </c>
       <c r="G195" s="5" t="n">
-        <v>-0.27627</v>
+        <v>0.040492</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -15800,17 +15818,17 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>Total expenses</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Net loss for the year - - -</t>
+          <t>Total expenses total</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -15819,10 +15837,10 @@
         </is>
       </c>
       <c r="F196" s="5" t="n">
-        <v>-0.206857</v>
+        <v>0.210281</v>
       </c>
       <c r="G196" s="5" t="n">
-        <v>-0.206857</v>
+        <v>0.224056</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -15858,25 +15876,29 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2018 total</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
+          <t>Interest income total</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F197" s="5" t="n">
-        <v>0.978024</v>
+        <v>0.008433</v>
       </c>
       <c r="G197" s="5" t="n">
-        <v>-0.483127</v>
+        <v>0.017199</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -15912,27 +15934,29 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Common shares issued in Initial</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Common shares issued in Initial</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
+          <t>Loss per share - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F198" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2e-08</v>
+      </c>
+      <c r="G198" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -15968,12 +15992,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Public Offering</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Issuance costs 3 - (107,537) -</t>
+          <t>Weighted average number of common shares outstanding – basic and diluted</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -15983,12 +16007,10 @@
         </is>
       </c>
       <c r="F199" s="5" t="n">
-        <v>-0.107537</v>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.598901</v>
+      </c>
+      <c r="G199" s="5" t="n">
+        <v>10</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -16024,12 +16046,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Public Offering</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Broker options issued 3 - (52,907) 52,907</t>
+          <t>Balance as at December 31, 19,030,780 1,265,595 195,556</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -16038,15 +16060,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F200" s="5" t="n">
+        <v>1.184881</v>
+      </c>
+      <c r="G200" s="5" t="n">
+        <v>-0.27627</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -16082,27 +16100,29 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Public Offering</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Stock based compensation 4 - - 142,649</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr"/>
+          <t>Net loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F201" s="5" t="n">
-        <v>0.142649</v>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.206857</v>
+      </c>
+      <c r="G201" s="5" t="n">
+        <v>-0.206857</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -16138,29 +16158,25 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Public Offering</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Net loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>2018 total</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F202" s="5" t="n">
-        <v>-0.201848</v>
+        <v>0.978024</v>
       </c>
       <c r="G202" s="5" t="n">
-        <v>-0.201848</v>
+        <v>-0.483127</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -16196,12 +16212,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Public Offering</t>
+          <t>Common shares issued in Initial</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Public Offering total</t>
+          <t>Common shares issued in Initial</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -16211,10 +16227,12 @@
         </is>
       </c>
       <c r="F203" s="5" t="n">
-        <v>11848.812018</v>
-      </c>
-      <c r="G203" s="5" t="n">
-        <v>-0.27627</v>
+        <v>1</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -16250,20 +16268,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>From the Date of</t>
+          <t>Public Offering</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Year ended Incorporation (June</t>
+          <t>Issuance costs 3 - (107,537) -</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
-      <c r="E204" s="5" t="n">
-        <v>0.002017</v>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F204" s="5" t="n">
-        <v>5e-06</v>
+        <v>-0.107537</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -16304,20 +16324,24 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>From the Date of</t>
+          <t>Public Offering</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>December 31, 2018 to December</t>
+          <t>Broker options issued 3 - (52,907) 52,907</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
-      <c r="E205" s="5" t="n">
-        <v>0.002017</v>
-      </c>
-      <c r="F205" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -16358,26 +16382,22 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Public Offering</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Interest income (Note 7) $</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Stock based compensation 4 - - 142,649</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F206" s="5" t="n">
-        <v>0.008433</v>
+        <v>0.142649</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -16418,29 +16438,29 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Public Offering</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Professional fees $</t>
+          <t>Net loss for the year - - -</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E207" s="5" t="n">
-        <v>0.06425</v>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F207" s="5" t="n">
-        <v>0.014793</v>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.201848</v>
+      </c>
+      <c r="G207" s="5" t="n">
+        <v>-0.201848</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -16476,25 +16496,25 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Public Offering</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Listing Fees</t>
+          <t>Public Offering total</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
-      <c r="E208" s="5" t="n">
-        <v>0.009809</v>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F208" s="5" t="n">
-        <v>0.016595</v>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>11848.812018</v>
+      </c>
+      <c r="G208" s="5" t="n">
+        <v>-0.27627</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -16530,26 +16550,20 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>From the Date of</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Depreciation (note 8)</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Year ended Incorporation (June</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" s="5" t="n">
+        <v>0.002017</v>
       </c>
       <c r="F209" s="5" t="n">
-        <v>0.00014</v>
+        <v>5e-06</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
@@ -16590,20 +16604,20 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>From the Date of</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>General and office</t>
+          <t>December 31, 2018 to December</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
       <c r="E210" s="5" t="n">
-        <v>0.000363</v>
+        <v>0.002017</v>
       </c>
       <c r="F210" s="5" t="n">
-        <v>0.036104</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
@@ -16644,22 +16658,26 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr"/>
+          <t>Interest income (Note 7) $</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F211" s="5" t="n">
-        <v>0.142649</v>
+        <v>0.008433</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
@@ -16705,19 +16723,19 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Total expenses</t>
+          <t>Professional fees $</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E212" s="5" t="n">
-        <v>0.074422</v>
+        <v>0.06425</v>
       </c>
       <c r="F212" s="5" t="n">
-        <v>0.210281</v>
+        <v>0.014793</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
@@ -16763,19 +16781,15 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Listing Fees</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
       <c r="E213" s="5" t="n">
-        <v>-0.074422</v>
+        <v>0.009809</v>
       </c>
       <c r="F213" s="5" t="n">
-        <v>-0.201848</v>
+        <v>0.016595</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
@@ -16816,17 +16830,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss per share (basic and diluted) $</t>
+          <t>Depreciation (note 8)</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -16835,7 +16849,7 @@
         </is>
       </c>
       <c r="F214" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.00014</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
@@ -16876,22 +16890,20 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>shares outstanding (basic and</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>shares outstanding (basic and diluted)</t>
+          <t>General and office</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E215" s="5" t="n">
+        <v>0.000363</v>
       </c>
       <c r="F215" s="5" t="n">
-        <v>8.598901</v>
+        <v>0.036104</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
@@ -16932,20 +16944,22 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>shares outstanding (basic and</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>shares outstanding (basic and total</t>
+          <t>Stock-based compensation</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
-      <c r="E216" s="5" t="n">
-        <v>0.002017</v>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F216" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.142649</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
@@ -16984,22 +16998,26 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr"/>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Balance at incorporation (June - $ - $ - $</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr"/>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E217" s="5" t="n">
+        <v>0.074422</v>
+      </c>
+      <c r="F217" s="5" t="n">
+        <v>0.210281</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
@@ -17040,20 +17058,24 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>equity total</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr"/>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E218" s="5" t="n">
-        <v>0.002017</v>
+        <v>-0.074422</v>
       </c>
       <c r="F218" s="5" t="n">
-        <v>5e-06</v>
+        <v>-0.201848</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
@@ -17094,22 +17116,26 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>equity</t>
+          <t>Net loss and comprehensive loss</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Issuance of common shares 9,030,780 451,539 -</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr"/>
-      <c r="E219" s="5" t="n">
-        <v>0.451539</v>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss and comprehensive loss per share (basic and diluted) $</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F219" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -17150,12 +17176,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>equity</t>
+          <t>shares outstanding (basic and</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>(Note</t>
+          <t>shares outstanding (basic and diluted)</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -17165,7 +17191,7 @@
         </is>
       </c>
       <c r="F220" s="5" t="n">
-        <v>3e-06</v>
+        <v>8.598901</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
@@ -17206,22 +17232,20 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>equity</t>
+          <t>shares outstanding (basic and</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Share issuance costs (Note 3) - (25,500)</t>
+          <t>shares outstanding (basic and total</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
       <c r="E221" s="5" t="n">
-        <v>-0.0255</v>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002017</v>
+      </c>
+      <c r="F221" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -17260,26 +17284,22 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>equity</t>
-        </is>
-      </c>
+      <c r="B222" t="inlineStr"/>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Net loss for the period - - -</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E222" s="5" t="n">
-        <v>-0.074422</v>
-      </c>
-      <c r="F222" s="5" t="n">
-        <v>-0.074422</v>
+          <t>Balance at incorporation (June - $ - $ - $</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
@@ -17325,15 +17345,15 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2017 9,030,780 $ 426,039 $ - $</t>
+          <t>equity total</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
       <c r="E223" s="5" t="n">
-        <v>0.351617</v>
+        <v>0.002017</v>
       </c>
       <c r="F223" s="5" t="n">
-        <v>-0.074422</v>
+        <v>5e-06</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -17372,18 +17392,24 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr"/>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>equity</t>
+        </is>
+      </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Balance at January 1, 2018 9,030,780 $ 426,039 $ - $</t>
+          <t>Issuance of common shares 9,030,780 451,539 -</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
       <c r="E224" s="5" t="n">
-        <v>0.351617</v>
-      </c>
-      <c r="F224" s="5" t="n">
-        <v>-0.074422</v>
+        <v>0.451539</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
@@ -17422,20 +17448,24 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr"/>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>equity</t>
+        </is>
+      </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Initial public offering (Note 3) 10,000,000 1,000,000 -</t>
+          <t>(Note</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
-      <c r="E225" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F225" s="5" t="n">
+        <v>3e-06</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
@@ -17474,15 +17504,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr"/>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>equity</t>
+        </is>
+      </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Issuance costs (Note 3) - (107,537) -</t>
+          <t>Share issuance costs (Note 3) - (25,500)</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
       <c r="E226" s="5" t="n">
-        <v>-0.107537</v>
+        <v>-0.0255</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17526,22 +17560,26 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr"/>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>equity</t>
+        </is>
+      </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Fair value of agent options - (52,907) 52,907</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss for the period - - -</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E227" s="5" t="n">
+        <v>-0.074422</v>
+      </c>
+      <c r="F227" s="5" t="n">
+        <v>-0.074422</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
@@ -17580,20 +17618,22 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr"/>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>equity</t>
+        </is>
+      </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Stock-based compensation - - 142,649</t>
+          <t>Balance, December 31, 2017 9,030,780 $ 426,039 $ - $</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
       <c r="E228" s="5" t="n">
-        <v>0.142649</v>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.351617</v>
+      </c>
+      <c r="F228" s="5" t="n">
+        <v>-0.074422</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
@@ -17635,19 +17675,15 @@
       <c r="B229" t="inlineStr"/>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Net loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance at January 1, 2018 9,030,780 $ 426,039 $ - $</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
       <c r="E229" s="5" t="n">
-        <v>-0.201848</v>
+        <v>0.351617</v>
       </c>
       <c r="F229" s="5" t="n">
-        <v>-0.201848</v>
+        <v>-0.074422</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
@@ -17689,42 +17725,658 @@
       <c r="B230" t="inlineStr"/>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2018 19,030,780 $ 1,265,595 $ 195,556 $</t>
+          <t>Initial public offering (Note 3) 10,000,000 1,000,000 -</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
       <c r="E230" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr"/>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Issuance costs (Note 3) - (107,537) -</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" s="5" t="n">
+        <v>-0.107537</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr"/>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Fair value of agent options - (52,907) 52,907</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr"/>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Stock-based compensation - - 142,649</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" s="5" t="n">
+        <v>0.142649</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr"/>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Net loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E234" s="5" t="n">
+        <v>-0.201848</v>
+      </c>
+      <c r="F234" s="5" t="n">
+        <v>-0.201848</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr"/>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2018 19,030,780 $ 1,265,595 $ 195,556 $</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" s="5" t="n">
         <v>1.184881</v>
       </c>
-      <c r="F230" s="5" t="n">
+      <c r="F235" s="5" t="n">
         <v>-0.27627</v>
       </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L230" t="inlineStr">
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Professional fees $</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E236" s="5" t="n">
+        <v>0.06425</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Bank fees</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" s="5" t="n">
+        <v>0.000363</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E238" s="5" t="n">
+        <v>0.074422</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Net income and comprehensive income (loss) $</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E239" s="5" t="n">
+        <v>-0.074422</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Net loss per</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Net loss per share $</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Net loss per</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Weighted average number of units outstanding</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
         <is>
           <t>-</t>
         </is>
